--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/WISCONSIN_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/WISCONSIN_2016.xlsx
@@ -2317,7 +2317,7 @@
         <v>76</v>
       </c>
       <c r="D109">
-        <v>0.009236752552260573</v>
+        <v>0.009236752552260571</v>
       </c>
     </row>
     <row r="110">
@@ -2353,7 +2353,7 @@
         <v>76</v>
       </c>
       <c r="D111">
-        <v>0.009236752552260573</v>
+        <v>0.009236752552260571</v>
       </c>
     </row>
     <row r="112">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C123">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C224">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C617">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C645">
@@ -18751,7 +18751,7 @@
         <v>78</v>
       </c>
       <c r="D1022">
-        <v>0.009479824987846379</v>
+        <v>0.009479824987846381</v>
       </c>
     </row>
     <row r="1023">
